--- a/Телефоны_компаний_по_ИНН.xlsx
+++ b/Телефоны_компаний_по_ИНН.xlsx
@@ -1011,7 +1011,7 @@
       <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>СПб, Полевая Сабировская 3Е; ОГРН 1237800137288</t>
+          <t>СПб, Полевая Сабировская 3Е; ОГРН 1237800137288; возможный сайт metpromserv.ru (НЕ подтверждён — проверить)</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr"/>
@@ -1300,33 +1300,37 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>ООО "НИДУС"</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>7842498887</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>191144 СПб, 10-я Советская 19А; ОГРН 1137847237791; возможный сайт nidus-rem.ru (не подтверждён)</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>sbis.ru/contragents/7842498887/781301001</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>+7 (812) 942-88-04; 8-800-200-67-06</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>info@nidus-rem.ru; nidus-rem.ru; 191144 СПб, 10-я Советская 19А пом.3-Н; ОГРН 1137847237791; ремонт квартир</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>nidus-rem.ru/kontakty (ИНН/ОГРН/адрес совпали)</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>высокая (ИНН совпал)</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1628,37 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>ООО "ПРОФИЛЬ-ДЕКОР"</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>7838499969</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>196240 СПб, Предпортовая ул. 6; ОГРН 1147847009881; профиль на b2b-center.ru</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>+7 (931) 238-95-81</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>196240 СПб, Предпортовая ул. 6 к.7; ОГРН 1147847009881; ген.дир. Чегодаев О.В.; металлические двери и окна</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Яндекс.Карты (карточка по адресу Предпортовая 6к7)</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>высокая (адрес совпал с ЕГРЮЛ)</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3964,7 @@
         </is>
       </c>
       <c r="B4" s="15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -3962,7 +3974,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6">
